--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/项目背景信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/项目背景信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,6 +548,94 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>background</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>客户项目背景</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>客户计划 Q3 上线 384 节点训练集群，替代现有 GPU 租赁方案，要求算力自主可控与液冷节能。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>客户项目目标</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>建设 384 节点昇腾训练集群，支持大模型训练与推理业务，实现算力自主可控。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>客户项目范围</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>算力底座（Atlas 900 A3 SuperPoD）+ 网络（400G RoCE）+ 存储（OceanStor）+ 液冷系统，含机房改造与上电。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>客户项目计划</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>客户里程碑：2026-06-01 机房就绪 → 2026-07-20 到货 → 2026-08-10 上线；与第 12 章计划联动</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/项目背景信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/项目背景信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,6 +636,94 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>background</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>客户项目背景</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>客户计划 Q3 上线 384 节点训练集群，替代现有 GPU 租赁方案，要求算力自主可控与液冷节能。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>客户项目目标</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>建设 384 节点昇腾训练集群，支持大模型训练与推理业务，实现算力自主可控。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>客户项目范围</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>算力底座（Atlas 900 A3 SuperPoD）+ 网络（400G RoCE）+ 存储（OceanStor）+ 液冷系统，含机房改造与上电。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>客户项目计划</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>客户里程碑：2026-06-01 机房就绪 → 2026-07-20 到货 → 2026-08-10 上线；与第 12 章计划联动</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/项目背景信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/项目背景信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +724,94 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>background</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>客户项目背景</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>客户计划 Q3 上线 384 节点训练集群，替代现有 GPU 租赁方案，要求算力自主可控与液冷节能。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>goal</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>客户项目目标</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>建设 384 节点昇腾训练集群，支持大模型训练与推理业务，实现算力自主可控。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>客户项目范围</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>算力底座（Atlas 900 A3 SuperPoD）+ 网络（400G RoCE）+ 存储（OceanStor）+ 液冷系统，含机房改造与上电。</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>客户项目计划</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>客户里程碑：2026-06-01 机房就绪 → 2026-07-20 到货 → 2026-08-10 上线；与第 12 章计划联动</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
